--- a/static/data/confidence_indices.xlsx
+++ b/static/data/confidence_indices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I443"/>
+  <dimension ref="A1:I444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11736,25 +11736,54 @@
         <v>81.81818181818183</v>
       </c>
       <c r="C443" t="n">
-        <v>72.72727272727273</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D443" t="n">
-        <v>25</v>
+        <v>23.07692307692308</v>
       </c>
       <c r="E443" t="n">
-        <v>23.07692307692308</v>
+        <v>20</v>
       </c>
       <c r="F443" t="n">
-        <v>45.45454545454545</v>
+        <v>50</v>
       </c>
       <c r="G443" t="n">
-        <v>76.92307692307693</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="H443" t="n">
         <v>58.33333333333334</v>
       </c>
       <c r="I443" t="n">
-        <v>7.692307692307693</v>
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B444" t="n">
+        <v>54.54545454545454</v>
+      </c>
+      <c r="C444" t="n">
+        <v>57.89473684210527</v>
+      </c>
+      <c r="D444" t="n">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="E444" t="n">
+        <v>36.36363636363637</v>
+      </c>
+      <c r="F444" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="G444" t="n">
+        <v>80</v>
+      </c>
+      <c r="H444" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="I444" t="n">
+        <v>52.17391304347826</v>
       </c>
     </row>
   </sheetData>
